--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:15:24+00:00</t>
+    <t>2026-09-02T14:33:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T14:33:35+00:00</t>
+    <t>2026-09-02T15:03:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1237,7 +1237,7 @@
     <t>biomarker</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/uv/genomics-reporting/StructureDefinition/molecular-biomarker)
+    <t xml:space="preserve">Reference(https://www.medizininformatik-initiative.de/fhir/ext/modul-molgen/StructureDefinition/mii-pr-molgen-molekularer-biomarker)
 </t>
   </si>
   <si>
@@ -1720,7 +1720,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="99.51171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="108.1015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-02T15:03:15+00:00</t>
+    <t>2026-09-03T06:40:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:40:42+00:00</t>
+    <t>2026-09-03T06:57:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T06:57:15+00:00</t>
+    <t>2026-09-03T07:38:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:38:27+00:00</t>
+    <t>2026-09-03T07:56:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T07:56:27+00:00</t>
+    <t>2026-09-03T08:11:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
+++ b/branches/docs/upstream-genomics-reporting/StructureDefinition-mii-pr-molgen-molekulargenetischer-befundbericht.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T08:11:50+00:00</t>
+    <t>2026-09-03T08:25:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
